--- a/data.mn/public/datasets/mrpam-petroleum-production.xlsx
+++ b/data.mn/public/datasets/mrpam-petroleum-production.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,13 +26,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,8 +56,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,26 +426,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>production_barrels</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>export_barrels</t>
         </is>
@@ -441,155 +459,729 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>317091</v>
+        <v>528388</v>
       </c>
       <c r="D2" t="n">
-        <v>284063</v>
+        <v>519260</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>298844</v>
+        <v>469032</v>
       </c>
       <c r="D3" t="n">
-        <v>311504</v>
+        <v>435559</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>327015</v>
+        <v>511189</v>
       </c>
       <c r="D4" t="n">
-        <v>322496</v>
+        <v>467307</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>308528</v>
+        <v>496377</v>
       </c>
       <c r="D5" t="n">
-        <v>255271</v>
+        <v>468414</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>309128</v>
+        <v>504245</v>
       </c>
       <c r="D6" t="n">
-        <v>346300</v>
+        <v>487420</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>311758</v>
+        <v>482447</v>
       </c>
       <c r="D7" t="n">
-        <v>296975</v>
+        <v>480475</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>306600</v>
+        <v>492037</v>
       </c>
       <c r="D8" t="n">
-        <v>298486</v>
+        <v>425415</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>304288</v>
+        <v>414776</v>
       </c>
       <c r="D9" t="n">
-        <v>272993</v>
+        <v>336288</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>322155</v>
+        <v>51634</v>
       </c>
       <c r="D10" t="n">
-        <v>315945</v>
+        <v>81278</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>312569</v>
+        <v>284336</v>
       </c>
       <c r="D11" t="n">
-        <v>273827</v>
+        <v>322724</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>389883</v>
+      </c>
+      <c r="D12" t="n">
+        <v>312552</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>37746</v>
+      </c>
+      <c r="D13" t="n">
+        <v>99876</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>347805</v>
+      </c>
+      <c r="D14" t="n">
+        <v>359232</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>454538</v>
+      </c>
+      <c r="D15" t="n">
+        <v>499389</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>425084</v>
+      </c>
+      <c r="D16" t="n">
+        <v>428311</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>417314</v>
+      </c>
+      <c r="D17" t="n">
+        <v>364944</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" t="n">
+        <v>410195</v>
+      </c>
+      <c r="D18" t="n">
+        <v>432823</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B19" t="n">
         <v>12</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C19" t="n">
+        <v>428119</v>
+      </c>
+      <c r="D19" t="n">
+        <v>414179</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>430646</v>
+      </c>
+      <c r="D20" t="n">
+        <v>393310</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>354053</v>
+      </c>
+      <c r="D21" t="n">
+        <v>368359</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>402971</v>
+      </c>
+      <c r="D22" t="n">
+        <v>418535</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>404419</v>
+      </c>
+      <c r="D23" t="n">
+        <v>394184</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>427321</v>
+      </c>
+      <c r="D24" t="n">
+        <v>415226</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>415058</v>
+      </c>
+      <c r="D25" t="n">
+        <v>395403</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" t="n">
+        <v>422488</v>
+      </c>
+      <c r="D26" t="n">
+        <v>402896</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>410287</v>
+      </c>
+      <c r="D27" t="n">
+        <v>385602</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="n">
+        <v>410884</v>
+      </c>
+      <c r="D28" t="n">
+        <v>420693</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="n">
+        <v>382824</v>
+      </c>
+      <c r="D29" t="n">
+        <v>359696</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B30" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" t="n">
+        <v>388303</v>
+      </c>
+      <c r="D30" t="n">
+        <v>376755</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>366669</v>
+      </c>
+      <c r="D31" t="n">
+        <v>365146</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>341269</v>
+      </c>
+      <c r="D32" t="n">
+        <v>320211</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>319557</v>
+      </c>
+      <c r="D33" t="n">
+        <v>315296</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>353497</v>
+      </c>
+      <c r="D34" t="n">
+        <v>354380</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>333425</v>
+      </c>
+      <c r="D35" t="n">
+        <v>341655</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B36" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" t="n">
+        <v>278922</v>
+      </c>
+      <c r="D36" t="n">
+        <v>294110</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B37" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" t="n">
+        <v>337317</v>
+      </c>
+      <c r="D37" t="n">
+        <v>315416</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" t="n">
+        <v>350264</v>
+      </c>
+      <c r="D38" t="n">
+        <v>358505</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B39" t="n">
+        <v>9</v>
+      </c>
+      <c r="C39" t="n">
+        <v>331236</v>
+      </c>
+      <c r="D39" t="n">
+        <v>336406</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B40" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" t="n">
+        <v>335337</v>
+      </c>
+      <c r="D40" t="n">
+        <v>335480</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B41" t="n">
+        <v>11</v>
+      </c>
+      <c r="C41" t="n">
+        <v>342334</v>
+      </c>
+      <c r="D41" t="n">
+        <v>328206</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B42" t="n">
+        <v>12</v>
+      </c>
+      <c r="C42" t="n">
+        <v>344625</v>
+      </c>
+      <c r="D42" t="n">
+        <v>294567</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>317091</v>
+      </c>
+      <c r="D43" t="n">
+        <v>284063</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>298844</v>
+      </c>
+      <c r="D44" t="n">
+        <v>311504</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="n">
+        <v>327015</v>
+      </c>
+      <c r="D45" t="n">
+        <v>322496</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>308528</v>
+      </c>
+      <c r="D46" t="n">
+        <v>255271</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" t="n">
+        <v>309128</v>
+      </c>
+      <c r="D47" t="n">
+        <v>346300</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="n">
+        <v>311758</v>
+      </c>
+      <c r="D48" t="n">
+        <v>296975</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" t="n">
+        <v>306600</v>
+      </c>
+      <c r="D49" t="n">
+        <v>298486</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B50" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" t="n">
+        <v>304288</v>
+      </c>
+      <c r="D50" t="n">
+        <v>272993</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B51" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" t="n">
+        <v>322155</v>
+      </c>
+      <c r="D51" t="n">
+        <v>315945</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B52" t="n">
+        <v>11</v>
+      </c>
+      <c r="C52" t="n">
+        <v>312569</v>
+      </c>
+      <c r="D52" t="n">
+        <v>273827</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B53" t="n">
+        <v>12</v>
+      </c>
+      <c r="C53" t="n">
         <v>322625</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D53" t="n">
         <v>271712</v>
       </c>
     </row>
@@ -604,26 +1196,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>он</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>сар</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>олборлолт_баррель</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>экспорт_баррель</t>
         </is>
@@ -631,155 +1229,729 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>317091</v>
+        <v>528388</v>
       </c>
       <c r="D2" t="n">
-        <v>284063</v>
+        <v>519260</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>298844</v>
+        <v>469032</v>
       </c>
       <c r="D3" t="n">
-        <v>311504</v>
+        <v>435559</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>327015</v>
+        <v>511189</v>
       </c>
       <c r="D4" t="n">
-        <v>322496</v>
+        <v>467307</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>308528</v>
+        <v>496377</v>
       </c>
       <c r="D5" t="n">
-        <v>255271</v>
+        <v>468414</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>309128</v>
+        <v>504245</v>
       </c>
       <c r="D6" t="n">
-        <v>346300</v>
+        <v>487420</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>311758</v>
+        <v>482447</v>
       </c>
       <c r="D7" t="n">
-        <v>296975</v>
+        <v>480475</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>306600</v>
+        <v>492037</v>
       </c>
       <c r="D8" t="n">
-        <v>298486</v>
+        <v>425415</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>304288</v>
+        <v>414776</v>
       </c>
       <c r="D9" t="n">
-        <v>272993</v>
+        <v>336288</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>322155</v>
+        <v>51634</v>
       </c>
       <c r="D10" t="n">
-        <v>315945</v>
+        <v>81278</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>312569</v>
+        <v>284336</v>
       </c>
       <c r="D11" t="n">
-        <v>273827</v>
+        <v>322724</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>389883</v>
+      </c>
+      <c r="D12" t="n">
+        <v>312552</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>37746</v>
+      </c>
+      <c r="D13" t="n">
+        <v>99876</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>347805</v>
+      </c>
+      <c r="D14" t="n">
+        <v>359232</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>454538</v>
+      </c>
+      <c r="D15" t="n">
+        <v>499389</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>425084</v>
+      </c>
+      <c r="D16" t="n">
+        <v>428311</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>417314</v>
+      </c>
+      <c r="D17" t="n">
+        <v>364944</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" t="n">
+        <v>410195</v>
+      </c>
+      <c r="D18" t="n">
+        <v>432823</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B19" t="n">
         <v>12</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C19" t="n">
+        <v>428119</v>
+      </c>
+      <c r="D19" t="n">
+        <v>414179</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>430646</v>
+      </c>
+      <c r="D20" t="n">
+        <v>393310</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>354053</v>
+      </c>
+      <c r="D21" t="n">
+        <v>368359</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>402971</v>
+      </c>
+      <c r="D22" t="n">
+        <v>418535</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>404419</v>
+      </c>
+      <c r="D23" t="n">
+        <v>394184</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>427321</v>
+      </c>
+      <c r="D24" t="n">
+        <v>415226</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>415058</v>
+      </c>
+      <c r="D25" t="n">
+        <v>395403</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" t="n">
+        <v>422488</v>
+      </c>
+      <c r="D26" t="n">
+        <v>402896</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>410287</v>
+      </c>
+      <c r="D27" t="n">
+        <v>385602</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="n">
+        <v>410884</v>
+      </c>
+      <c r="D28" t="n">
+        <v>420693</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="n">
+        <v>382824</v>
+      </c>
+      <c r="D29" t="n">
+        <v>359696</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B30" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" t="n">
+        <v>388303</v>
+      </c>
+      <c r="D30" t="n">
+        <v>376755</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>366669</v>
+      </c>
+      <c r="D31" t="n">
+        <v>365146</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>341269</v>
+      </c>
+      <c r="D32" t="n">
+        <v>320211</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>319557</v>
+      </c>
+      <c r="D33" t="n">
+        <v>315296</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>353497</v>
+      </c>
+      <c r="D34" t="n">
+        <v>354380</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>333425</v>
+      </c>
+      <c r="D35" t="n">
+        <v>341655</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B36" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" t="n">
+        <v>278922</v>
+      </c>
+      <c r="D36" t="n">
+        <v>294110</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B37" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" t="n">
+        <v>337317</v>
+      </c>
+      <c r="D37" t="n">
+        <v>315416</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" t="n">
+        <v>350264</v>
+      </c>
+      <c r="D38" t="n">
+        <v>358505</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B39" t="n">
+        <v>9</v>
+      </c>
+      <c r="C39" t="n">
+        <v>331236</v>
+      </c>
+      <c r="D39" t="n">
+        <v>336406</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B40" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" t="n">
+        <v>335337</v>
+      </c>
+      <c r="D40" t="n">
+        <v>335480</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B41" t="n">
+        <v>11</v>
+      </c>
+      <c r="C41" t="n">
+        <v>342334</v>
+      </c>
+      <c r="D41" t="n">
+        <v>328206</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B42" t="n">
+        <v>12</v>
+      </c>
+      <c r="C42" t="n">
+        <v>344625</v>
+      </c>
+      <c r="D42" t="n">
+        <v>294567</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>317091</v>
+      </c>
+      <c r="D43" t="n">
+        <v>284063</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>298844</v>
+      </c>
+      <c r="D44" t="n">
+        <v>311504</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="n">
+        <v>327015</v>
+      </c>
+      <c r="D45" t="n">
+        <v>322496</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>308528</v>
+      </c>
+      <c r="D46" t="n">
+        <v>255271</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" t="n">
+        <v>309128</v>
+      </c>
+      <c r="D47" t="n">
+        <v>346300</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="n">
+        <v>311758</v>
+      </c>
+      <c r="D48" t="n">
+        <v>296975</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" t="n">
+        <v>306600</v>
+      </c>
+      <c r="D49" t="n">
+        <v>298486</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B50" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" t="n">
+        <v>304288</v>
+      </c>
+      <c r="D50" t="n">
+        <v>272993</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B51" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" t="n">
+        <v>322155</v>
+      </c>
+      <c r="D51" t="n">
+        <v>315945</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B52" t="n">
+        <v>11</v>
+      </c>
+      <c r="C52" t="n">
+        <v>312569</v>
+      </c>
+      <c r="D52" t="n">
+        <v>273827</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B53" t="n">
+        <v>12</v>
+      </c>
+      <c r="C53" t="n">
         <v>322625</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D53" t="n">
         <v>271712</v>
       </c>
     </row>

--- a/data.mn/public/datasets/mrpam-petroleum-production.xlsx
+++ b/data.mn/public/datasets/mrpam-petroleum-production.xlsx
@@ -1,19 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data EN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Өгөгдөл MN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data EN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Өгөгдөл MN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data EN'!$A$1:$D$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Өгөгдөл MN'!$A$1:$D$67</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -417,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -612,7 +609,6 @@
       <c r="C13" t="n">
         <v>33623</v>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -624,7 +620,6 @@
       <c r="C14" t="n">
         <v>17544</v>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -636,7 +631,6 @@
       <c r="C15" t="n">
         <v>9921</v>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -648,7 +642,6 @@
       <c r="C16" t="n">
         <v>9257</v>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -660,7 +653,6 @@
       <c r="C17" t="n">
         <v>1001</v>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -672,7 +664,6 @@
       <c r="C18" t="n">
         <v>1290</v>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1360,8 +1351,21 @@
         <v>287125</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" t="n">
+        <v>299729</v>
+      </c>
+      <c r="D68" t="n">
+        <v>234735</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1372,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1567,7 +1571,6 @@
       <c r="C13" t="n">
         <v>33623</v>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1579,7 +1582,6 @@
       <c r="C14" t="n">
         <v>17544</v>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1591,7 +1593,6 @@
       <c r="C15" t="n">
         <v>9921</v>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1603,7 +1604,6 @@
       <c r="C16" t="n">
         <v>9257</v>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1615,7 +1615,6 @@
       <c r="C17" t="n">
         <v>1001</v>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1627,7 +1626,6 @@
       <c r="C18" t="n">
         <v>1290</v>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2315,8 +2313,21 @@
         <v>287125</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" t="n">
+        <v>299729</v>
+      </c>
+      <c r="D68" t="n">
+        <v>234735</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>